--- a/finanzas/Finanzas_GMGP_2026.xlsx
+++ b/finanzas/Finanzas_GMGP_2026.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="169" formatCode="DD-MM-YYYY"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,12 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
       <color rgb="00595959"/>
       <sz val="11"/>
     </font>
@@ -179,7 +185,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -211,6 +217,11 @@
         <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -238,49 +249,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -304,6 +315,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -314,6 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1004,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1033,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1029,6 +1048,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -1044,6 +1064,7 @@
       </c>
     </row>
     <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -1087,6 +1108,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -1264,6 +1286,8 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -1343,6 +1367,8 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -1410,6 +1436,8 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
+    <row r="43"/>
     <row r="44">
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -1432,6 +1460,7 @@
       </c>
     </row>
     <row r="47" ht="26" customHeight="1"/>
+    <row r="48"/>
     <row r="49">
       <c r="B49" s="15" t="inlineStr">
         <is>
@@ -1447,6 +1476,7 @@
       </c>
     </row>
     <row r="51" ht="26" customHeight="1"/>
+    <row r="52"/>
     <row r="53">
       <c r="B53" s="15" t="inlineStr">
         <is>
@@ -1462,6 +1492,7 @@
       </c>
     </row>
     <row r="55" ht="26" customHeight="1"/>
+    <row r="56"/>
     <row r="57">
       <c r="B57" s="15" t="inlineStr">
         <is>
@@ -1477,6 +1508,7 @@
       </c>
     </row>
     <row r="59" ht="26" customHeight="1"/>
+    <row r="60"/>
     <row r="61">
       <c r="B61" s="15" t="inlineStr">
         <is>
@@ -1492,6 +1524,7 @@
       </c>
     </row>
     <row r="63" ht="26" customHeight="1"/>
+    <row r="64"/>
     <row r="65">
       <c r="B65" s="16" t="inlineStr">
         <is>
@@ -1571,6 +1604,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -1588,8 +1622,9 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>1 · Identidad de la empresa</t>
         </is>
@@ -1601,14 +1636,14 @@
           <t>Razón social</t>
         </is>
       </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>GM Growth Partners SpA</t>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>GM GROWTH PARTNERS SPA</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Ajústalo al nombre exacto de tu escritura.</t>
+          <t>Tal como sale en tus facturas electrónicas.</t>
         </is>
       </c>
     </row>
@@ -1618,9 +1653,9 @@
           <t>RUT</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>76.XXX.XXX-X</t>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>78.415.321-5</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -1635,12 +1670,16 @@
           <t>Giro</t>
         </is>
       </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>Servicios de marketing y desarrollo digital</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr"/>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>CONSULTORÍA COMERCIAL Y DESARROLLO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>El giro con el que facturas ante el SII.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1675,7 +1714,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>2 · Tasas tributarias vigentes</t>
         </is>
@@ -1687,7 +1726,7 @@
           <t>IVA</t>
         </is>
       </c>
-      <c r="B13" s="54" t="n">
+      <c r="B13" s="59" t="n">
         <v>0.19</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -1702,7 +1741,7 @@
           <t>Impuesto de Primera Categoría (IDPC)</t>
         </is>
       </c>
-      <c r="B14" s="54" t="n">
+      <c r="B14" s="59" t="n">
         <v>0.125</v>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -1717,7 +1756,7 @@
           <t>Tasa de PPM mensual</t>
         </is>
       </c>
-      <c r="B15" s="55" t="n">
+      <c r="B15" s="60" t="n">
         <v>0.00125</v>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -1732,7 +1771,7 @@
           <t>Retención de honorarios a terceros</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="61" t="n">
         <v>0.1525</v>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -1741,6 +1780,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -1748,8 +1788,9 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>3 · Saldos con los que parte el año</t>
         </is>
@@ -1785,8 +1826,9 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>4 · Valor de la UTM mes a mes</t>
         </is>
@@ -1930,12 +1972,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="inlineStr">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>UTA (UTM de diciembre × 12)</t>
         </is>
       </c>
-      <c r="B38" s="57">
+      <c r="B38" s="62">
         <f>B37*12</f>
         <v/>
       </c>
@@ -1945,8 +1987,9 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="47" t="inlineStr">
         <is>
           <t>5 · Tramos del Impuesto Global Complementario (tabla anual del SII)</t>
         </is>
@@ -1986,16 +2029,16 @@
       <c r="G41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="n">
+      <c r="A42" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="B42" s="58" t="n">
+      <c r="B42" s="63" t="n">
         <v>13.5</v>
       </c>
-      <c r="C42" s="59" t="n">
+      <c r="C42" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="60" t="n">
+      <c r="D42" s="65" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="26">
@@ -2008,16 +2051,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="n">
+      <c r="A43" s="63" t="n">
         <v>13.5</v>
       </c>
-      <c r="B43" s="58" t="n">
+      <c r="B43" s="63" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="59" t="n">
+      <c r="C43" s="64" t="n">
         <v>0.04</v>
       </c>
-      <c r="D43" s="60" t="n">
+      <c r="D43" s="65" t="n">
         <v>0.54</v>
       </c>
       <c r="E43" s="26">
@@ -2030,16 +2073,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="n">
+      <c r="A44" s="63" t="n">
         <v>30</v>
       </c>
-      <c r="B44" s="58" t="n">
+      <c r="B44" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="C44" s="59" t="n">
+      <c r="C44" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="D44" s="60" t="n">
+      <c r="D44" s="65" t="n">
         <v>1.74</v>
       </c>
       <c r="E44" s="26">
@@ -2052,16 +2095,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="n">
+      <c r="A45" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="B45" s="58" t="n">
+      <c r="B45" s="63" t="n">
         <v>70</v>
       </c>
-      <c r="C45" s="59" t="n">
+      <c r="C45" s="64" t="n">
         <v>0.135</v>
       </c>
-      <c r="D45" s="60" t="n">
+      <c r="D45" s="65" t="n">
         <v>4.49</v>
       </c>
       <c r="E45" s="26">
@@ -2074,16 +2117,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="n">
+      <c r="A46" s="63" t="n">
         <v>70</v>
       </c>
-      <c r="B46" s="58" t="n">
+      <c r="B46" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="C46" s="59" t="n">
+      <c r="C46" s="64" t="n">
         <v>0.23</v>
       </c>
-      <c r="D46" s="60" t="n">
+      <c r="D46" s="65" t="n">
         <v>11.14</v>
       </c>
       <c r="E46" s="26">
@@ -2096,16 +2139,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="n">
+      <c r="A47" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="B47" s="58" t="n">
+      <c r="B47" s="63" t="n">
         <v>120</v>
       </c>
-      <c r="C47" s="59" t="n">
+      <c r="C47" s="64" t="n">
         <v>0.304</v>
       </c>
-      <c r="D47" s="60" t="n">
+      <c r="D47" s="65" t="n">
         <v>17.8</v>
       </c>
       <c r="E47" s="26">
@@ -2118,16 +2161,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="n">
+      <c r="A48" s="63" t="n">
         <v>120</v>
       </c>
-      <c r="B48" s="58" t="n">
+      <c r="B48" s="63" t="n">
         <v>310</v>
       </c>
-      <c r="C48" s="59" t="n">
+      <c r="C48" s="64" t="n">
         <v>0.35</v>
       </c>
-      <c r="D48" s="60" t="n">
+      <c r="D48" s="65" t="n">
         <v>23.32</v>
       </c>
       <c r="E48" s="26">
@@ -2140,18 +2183,18 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="n">
+      <c r="A49" s="63" t="n">
         <v>310</v>
       </c>
-      <c r="B49" s="58" t="inlineStr">
+      <c r="B49" s="63" t="inlineStr">
         <is>
           <t>y más</t>
         </is>
       </c>
-      <c r="C49" s="59" t="n">
+      <c r="C49" s="64" t="n">
         <v>0.4</v>
       </c>
-      <c r="D49" s="60" t="n">
+      <c r="D49" s="65" t="n">
         <v>38.82</v>
       </c>
       <c r="E49" s="26">
@@ -2170,8 +2213,9 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>6 · Tipos de documento de GASTO y su efecto tributario</t>
         </is>
@@ -2211,13 +2255,13 @@
           <t>Factura afecta</t>
         </is>
       </c>
-      <c r="B54" s="61" t="n">
+      <c r="B54" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="61" t="n">
+      <c r="C54" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="62" t="n">
+      <c r="D54" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="23" t="inlineStr">
@@ -2232,13 +2276,13 @@
           <t>Factura exenta o no afecta</t>
         </is>
       </c>
-      <c r="B55" s="62" t="n">
+      <c r="B55" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C55" s="62" t="n">
+      <c r="C55" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="62" t="n">
+      <c r="D55" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="23" t="inlineStr">
@@ -2253,13 +2297,13 @@
           <t>Boleta de honorarios recibida</t>
         </is>
       </c>
-      <c r="B56" s="62" t="n">
+      <c r="B56" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C56" s="62" t="n">
+      <c r="C56" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="61" t="n">
+      <c r="D56" s="66" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="23" t="inlineStr">
@@ -2274,13 +2318,13 @@
           <t>Boleta de venta</t>
         </is>
       </c>
-      <c r="B57" s="62" t="n">
+      <c r="B57" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C57" s="62" t="n">
+      <c r="C57" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="62" t="n">
+      <c r="D57" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="23" t="inlineStr">
@@ -2295,13 +2339,13 @@
           <t>Servicio digital extranjero</t>
         </is>
       </c>
-      <c r="B58" s="61" t="n">
+      <c r="B58" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="62" t="n">
+      <c r="C58" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="62" t="n">
+      <c r="D58" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="23" t="inlineStr">
@@ -2316,13 +2360,13 @@
           <t>Nota de crédito recibida</t>
         </is>
       </c>
-      <c r="B59" s="61" t="n">
+      <c r="B59" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="61" t="n">
+      <c r="C59" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="62" t="n">
+      <c r="D59" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -2337,13 +2381,13 @@
           <t>Sin documento</t>
         </is>
       </c>
-      <c r="B60" s="62" t="n">
+      <c r="B60" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="C60" s="62" t="n">
+      <c r="C60" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="62" t="n">
+      <c r="D60" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="23" t="inlineStr">
@@ -2360,7 +2404,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="43" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>7 · Tipos de documento de INGRESO</t>
         </is>
@@ -2392,7 +2436,7 @@
           <t>Factura afecta</t>
         </is>
       </c>
-      <c r="B64" s="61" t="n">
+      <c r="B64" s="66" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="23" t="inlineStr">
@@ -2407,7 +2451,7 @@
           <t>Factura exenta</t>
         </is>
       </c>
-      <c r="B65" s="62" t="n">
+      <c r="B65" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="23" t="inlineStr">
@@ -2422,7 +2466,7 @@
           <t>Factura de exportación</t>
         </is>
       </c>
-      <c r="B66" s="62" t="n">
+      <c r="B66" s="67" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="23" t="inlineStr">
@@ -2437,7 +2481,7 @@
           <t>Boleta de servicio</t>
         </is>
       </c>
-      <c r="B67" s="61" t="n">
+      <c r="B67" s="66" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="23" t="inlineStr">
@@ -2452,7 +2496,7 @@
           <t>Nota de crédito emitida</t>
         </is>
       </c>
-      <c r="B68" s="61" t="n">
+      <c r="B68" s="66" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="23" t="inlineStr">
@@ -2461,8 +2505,9 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
-      <c r="A70" s="43" t="inlineStr">
+      <c r="A70" s="47" t="inlineStr">
         <is>
           <t>8 · Listas de los menús desplegables (agrega filas si te faltan)</t>
         </is>
@@ -2485,148 +2530,156 @@
       <c r="F71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="63" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>Software y suscripciones</t>
         </is>
       </c>
-      <c r="B72" s="63" t="inlineStr">
+      <c r="B72" s="68" t="inlineStr">
         <is>
           <t>Transferencia</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="63" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>Subcontratos y freelance</t>
         </is>
       </c>
-      <c r="B73" s="63" t="inlineStr">
+      <c r="B73" s="68" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="68" t="inlineStr">
+        <is>
+          <t>Publicidad y medios</t>
+        </is>
+      </c>
+      <c r="B74" s="68" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="68" t="inlineStr">
+        <is>
+          <t>Honorarios profesionales</t>
+        </is>
+      </c>
+      <c r="B75" s="68" t="inlineStr">
         <is>
           <t>Tarjeta de crédito</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="63" t="inlineStr">
-        <is>
-          <t>Publicidad y medios</t>
-        </is>
-      </c>
-      <c r="B74" s="63" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="68" t="inlineStr">
+        <is>
+          <t>Contabilidad y legal</t>
+        </is>
+      </c>
+      <c r="B76" s="68" t="inlineStr">
         <is>
           <t>Tarjeta de débito</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="63" t="inlineStr">
-        <is>
-          <t>Honorarios profesionales</t>
-        </is>
-      </c>
-      <c r="B75" s="63" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="68" t="inlineStr">
+        <is>
+          <t>Arriendo y oficina</t>
+        </is>
+      </c>
+      <c r="B77" s="68" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="63" t="inlineStr">
-        <is>
-          <t>Contabilidad y legal</t>
-        </is>
-      </c>
-      <c r="B76" s="63" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="68" t="inlineStr">
+        <is>
+          <t>Servicios básicos e internet</t>
+        </is>
+      </c>
+      <c r="B78" s="68" t="inlineStr">
         <is>
           <t>Cheque</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="63" t="inlineStr">
-        <is>
-          <t>Arriendo y oficina</t>
-        </is>
-      </c>
-      <c r="B77" s="63" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="68" t="inlineStr">
+        <is>
+          <t>Equipamiento y hardware</t>
+        </is>
+      </c>
+      <c r="B79" s="68" t="inlineStr">
         <is>
           <t>Otro</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="63" t="inlineStr">
-        <is>
-          <t>Servicios básicos e internet</t>
-        </is>
-      </c>
-      <c r="B78" s="63" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="63" t="inlineStr">
-        <is>
-          <t>Equipamiento y hardware</t>
-        </is>
-      </c>
-      <c r="B79" s="63" t="n"/>
-    </row>
     <row r="80">
-      <c r="A80" s="63" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>Comisiones bancarias</t>
         </is>
       </c>
-      <c r="B80" s="63" t="n"/>
+      <c r="B80" s="68" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="63" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>Movilización y viáticos</t>
         </is>
       </c>
-      <c r="B81" s="63" t="n"/>
+      <c r="B81" s="68" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="63" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>Capacitación</t>
         </is>
       </c>
-      <c r="B82" s="63" t="n"/>
+      <c r="B82" s="68" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="63" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>Impuestos y patente municipal</t>
         </is>
       </c>
-      <c r="B83" s="63" t="n"/>
+      <c r="B83" s="68" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="63" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>Otros gastos</t>
         </is>
       </c>
-      <c r="B84" s="63" t="n"/>
+      <c r="B84" s="68" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="63" t="n"/>
-      <c r="B85" s="63" t="n"/>
+      <c r="A85" s="68" t="n"/>
+      <c r="B85" s="68" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="63" t="n"/>
-      <c r="B86" s="63" t="n"/>
+      <c r="A86" s="68" t="n"/>
+      <c r="B86" s="68" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="63" t="n"/>
-      <c r="B87" s="63" t="n"/>
+      <c r="A87" s="68" t="n"/>
+      <c r="B87" s="68" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="63" t="n"/>
-      <c r="B88" s="63" t="n"/>
+      <c r="A88" s="68" t="n"/>
+      <c r="B88" s="68" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2691,6 +2744,8 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -2757,6 +2812,8 @@
       <c r="J7" s="19" t="n"/>
       <c r="K7" s="19" t="n"/>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
@@ -3283,6 +3340,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -3290,6 +3348,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
@@ -3371,6 +3430,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -3395,6 +3455,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -3493,7 +3554,7 @@
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>TURISMO PALMENIA MABEL CÁRDENAS RODRÍGUEZ</t>
+          <t>TURISMO PALMENIA MABEL CÁRDENAS RODRÍGUEZ E.I.R.L.</t>
         </is>
       </c>
       <c r="E8" s="35" t="inlineStr">
@@ -3580,7 +3641,7 @@
         <v/>
       </c>
       <c r="I9" s="37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="25">
         <f>IF($B9="","",SUMIFS(Pagos!$E$8:$E$307,Pagos!$B$8:$B$307,$B9))</f>
@@ -10350,6 +10411,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -10374,6 +10436,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -10428,11 +10491,11 @@
     </row>
     <row r="8">
       <c r="A8" s="34" t="n">
-        <v>46207</v>
+        <v>46176</v>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>F-001</t>
+          <t>F-002</t>
         </is>
       </c>
       <c r="C8" s="42">
@@ -10443,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>238000</v>
+        <v>47000</v>
       </c>
       <c r="F8" s="25">
         <f>IF($E8="","",IFERROR(ROUND($E8*INDEX(Ingresos!$F$8:$F$157,MATCH($B8,Ingresos!$B$8:$B$157,0))/INDEX(Ingresos!$H$8:$H$157,MATCH($B8,Ingresos!$B$8:$B$157,0)),0),$E8))</f>
@@ -10451,10 +10514,14 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H8" s="35" t="inlineStr"/>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>Suscripción mensual · operación 162295206706</t>
+        </is>
+      </c>
       <c r="I8" s="41">
         <f>IF($A8="","",YEAR($A8))</f>
         <v/>
@@ -10471,7 +10538,7 @@
     </row>
     <row r="9">
       <c r="A9" s="34" t="n">
-        <v>46063</v>
+        <v>46204</v>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
@@ -10483,10 +10550,10 @@
         <v/>
       </c>
       <c r="D9" s="37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>141000</v>
+        <v>47000</v>
       </c>
       <c r="F9" s="25">
         <f>IF($E9="","",IFERROR(ROUND($E9*INDEX(Ingresos!$F$8:$F$157,MATCH($B9,Ingresos!$B$8:$B$157,0))/INDEX(Ingresos!$H$8:$H$157,MATCH($B9,Ingresos!$B$8:$B$157,0)),0),$E9))</f>
@@ -10494,10 +10561,14 @@
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>Transferencia</t>
-        </is>
-      </c>
-      <c r="H9" s="35" t="inlineStr"/>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>Suscripción mensual · operación 165795559415</t>
+        </is>
+      </c>
       <c r="I9" s="41">
         <f>IF($A9="","",YEAR($A9))</f>
         <v/>
@@ -10509,11 +10580,11 @@
     </row>
     <row r="10">
       <c r="A10" s="34" t="n">
-        <v>46248</v>
+        <v>46207</v>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>F-003</t>
+          <t>F-001</t>
         </is>
       </c>
       <c r="C10" s="42">
@@ -10524,7 +10595,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>750000</v>
+        <v>238000</v>
       </c>
       <c r="F10" s="25">
         <f>IF($E10="","",IFERROR(ROUND($E10*INDEX(Ingresos!$F$8:$F$157,MATCH($B10,Ingresos!$B$8:$B$157,0))/INDEX(Ingresos!$H$8:$H$157,MATCH($B10,Ingresos!$B$8:$B$157,0)),0),$E10))</f>
@@ -10535,7 +10606,11 @@
           <t>Transferencia</t>
         </is>
       </c>
-      <c r="H10" s="35" t="inlineStr"/>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>Transferencia recibida</t>
+        </is>
+      </c>
       <c r="I10" s="41">
         <f>IF($A10="","",YEAR($A10))</f>
         <v/>
@@ -10546,20 +10621,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="35" t="n"/>
+      <c r="A11" s="34" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
       <c r="C11" s="42">
         <f>IF($B11="","",IFERROR(INDEX(Ingresos!$D$8:$D$157,MATCH($B11,Ingresos!$B$8:$B$157,0)),"⚠ n° no existe"))</f>
         <v/>
       </c>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="36" t="n"/>
+      <c r="D11" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>47000</v>
+      </c>
       <c r="F11" s="25">
         <f>IF($E11="","",IFERROR(ROUND($E11*INDEX(Ingresos!$F$8:$F$157,MATCH($B11,Ingresos!$B$8:$B$157,0))/INDEX(Ingresos!$H$8:$H$157,MATCH($B11,Ingresos!$B$8:$B$157,0)),0),$E11))</f>
         <v/>
       </c>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>Suscripción mensual · operación 171532776354</t>
+        </is>
+      </c>
       <c r="I11" s="41">
         <f>IF($A11="","",YEAR($A11))</f>
         <v/>
@@ -10570,20 +10663,38 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="n"/>
-      <c r="B12" s="35" t="n"/>
+      <c r="A12" s="34" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
       <c r="C12" s="42">
         <f>IF($B12="","",IFERROR(INDEX(Ingresos!$D$8:$D$157,MATCH($B12,Ingresos!$B$8:$B$157,0)),"⚠ n° no existe"))</f>
         <v/>
       </c>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="36" t="n"/>
+      <c r="D12" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>750000</v>
+      </c>
       <c r="F12" s="25">
         <f>IF($E12="","",IFERROR(ROUND($E12*INDEX(Ingresos!$F$8:$F$157,MATCH($B12,Ingresos!$B$8:$B$157,0))/INDEX(Ingresos!$H$8:$H$157,MATCH($B12,Ingresos!$B$8:$B$157,0)),0),$E12))</f>
         <v/>
       </c>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>Transferencia recibida</t>
+        </is>
+      </c>
       <c r="I12" s="41">
         <f>IF($A12="","",YEAR($A12))</f>
         <v/>
@@ -17750,6 +17861,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -17770,10 +17882,11 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Formato esperado: fecha del documento · N° · tipo (define IVA, crédito y retención) · proveedor · categoría · monto tal como viene y si trae IVA adentro · si está pagado y cuándo. «¿Gasto aceptado?» = si el SII lo acepta como gasto de la empresa. Todo lo personal va en No (y en rigor no debería pasar por la cuenta de la empresa).</t>
-        </is>
-      </c>
-    </row>
+          <t>⚠ Los pagos al SII (PPM, IVA) NO van acá: son el impuesto mismo, y la planilla ya lo calcula en la hoja Mensual. Registrarlos como gasto los contaría dos veces. «¿Gasto aceptado?» = si el SII lo acepta como gasto de la empresa. Todo lo personal va en No (y en rigor no debería pasar por la cuenta de la empresa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -17887,271 +18000,481 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="26">
+      <c r="A8" s="43" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Servicio digital extranjero</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>Software y suscripciones</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat · suscripción</t>
+        </is>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>9401</v>
+      </c>
+      <c r="H8" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I8" s="45">
         <f>IF($G8="","",IF(AND($H8="Sí",IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C8,Parámetros!$A$54:$A$60,0)),0)=1),ROUND($G8/(1+Parámetros!$B$13),0),$G8))</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="45">
         <f>IF($G8="","",IF(IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C8,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I8*Parámetros!$B$13,0),0))</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="45">
         <f>IF($G8="","",IF(IFERROR(INDEX(Parámetros!$C$54:$C$60,MATCH($C8,Parámetros!$A$54:$A$60,0)),0)=1,$J8,0))</f>
         <v/>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="45">
         <f>IF($G8="","",IF(IFERROR(INDEX(Parámetros!$D$54:$D$60,MATCH($C8,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I8*Parámetros!$B$16,0),0))</f>
         <v/>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="45">
         <f>IF($G8="","",$I8+$J8)</f>
         <v/>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="45">
         <f>IF($G8="","",$M8-$L8)</f>
         <v/>
       </c>
-      <c r="O8" s="35" t="n"/>
-      <c r="P8" s="35" t="n"/>
-      <c r="Q8" s="34" t="n"/>
-      <c r="R8" s="35" t="n"/>
-      <c r="S8" s="41">
+      <c r="O8" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P8" s="44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="Q8" s="43" t="n">
+        <v>46209</v>
+      </c>
+      <c r="R8" s="44" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+      <c r="S8" s="46">
         <f>IF($A8="","",YEAR($A8))</f>
         <v/>
       </c>
-      <c r="T8" s="41">
+      <c r="T8" s="46">
         <f>IF($A8="","",MONTH($A8))</f>
         <v/>
       </c>
-      <c r="U8" s="41">
+      <c r="U8" s="46">
         <f>IF($Q8="","",YEAR($Q8))</f>
         <v/>
       </c>
-      <c r="V8" s="41">
+      <c r="V8" s="46">
         <f>IF($Q8="","",MONTH($Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="26">
+      <c r="A9" s="43" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Servicio digital extranjero</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>Software y suscripciones</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat · suscripción</t>
+        </is>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>36776</v>
+      </c>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I9" s="45">
         <f>IF($G9="","",IF(AND($H9="Sí",IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C9,Parámetros!$A$54:$A$60,0)),0)=1),ROUND($G9/(1+Parámetros!$B$13),0),$G9))</f>
         <v/>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="45">
         <f>IF($G9="","",IF(IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C9,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I9*Parámetros!$B$13,0),0))</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="45">
         <f>IF($G9="","",IF(IFERROR(INDEX(Parámetros!$C$54:$C$60,MATCH($C9,Parámetros!$A$54:$A$60,0)),0)=1,$J9,0))</f>
         <v/>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="45">
         <f>IF($G9="","",IF(IFERROR(INDEX(Parámetros!$D$54:$D$60,MATCH($C9,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I9*Parámetros!$B$16,0),0))</f>
         <v/>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="45">
         <f>IF($G9="","",$I9+$J9)</f>
         <v/>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="45">
         <f>IF($G9="","",$M9-$L9)</f>
         <v/>
       </c>
-      <c r="O9" s="35" t="n"/>
-      <c r="P9" s="35" t="n"/>
-      <c r="Q9" s="34" t="n"/>
-      <c r="R9" s="35" t="n"/>
-      <c r="S9" s="41">
+      <c r="O9" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P9" s="44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="Q9" s="43" t="n">
+        <v>46221</v>
+      </c>
+      <c r="R9" s="44" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+      <c r="S9" s="46">
         <f>IF($A9="","",YEAR($A9))</f>
         <v/>
       </c>
-      <c r="T9" s="41">
+      <c r="T9" s="46">
         <f>IF($A9="","",MONTH($A9))</f>
         <v/>
       </c>
-      <c r="U9" s="41">
+      <c r="U9" s="46">
         <f>IF($Q9="","",YEAR($Q9))</f>
         <v/>
       </c>
-      <c r="V9" s="41">
+      <c r="V9" s="46">
         <f>IF($Q9="","",MONTH($Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="26">
+      <c r="A10" s="43" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>Servicio digital extranjero</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>Airtable</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>Software y suscripciones</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>Airtable · suscripción</t>
+        </is>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>68586</v>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I10" s="45">
         <f>IF($G10="","",IF(AND($H10="Sí",IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C10,Parámetros!$A$54:$A$60,0)),0)=1),ROUND($G10/(1+Parámetros!$B$13),0),$G10))</f>
         <v/>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="45">
         <f>IF($G10="","",IF(IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C10,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I10*Parámetros!$B$13,0),0))</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="45">
         <f>IF($G10="","",IF(IFERROR(INDEX(Parámetros!$C$54:$C$60,MATCH($C10,Parámetros!$A$54:$A$60,0)),0)=1,$J10,0))</f>
         <v/>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="45">
         <f>IF($G10="","",IF(IFERROR(INDEX(Parámetros!$D$54:$D$60,MATCH($C10,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I10*Parámetros!$B$16,0),0))</f>
         <v/>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="45">
         <f>IF($G10="","",$I10+$J10)</f>
         <v/>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="45">
         <f>IF($G10="","",$M10-$L10)</f>
         <v/>
       </c>
-      <c r="O10" s="35" t="n"/>
-      <c r="P10" s="35" t="n"/>
-      <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="35" t="n"/>
-      <c r="S10" s="41">
+      <c r="O10" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P10" s="44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="Q10" s="43" t="n">
+        <v>46224</v>
+      </c>
+      <c r="R10" s="44" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+      <c r="S10" s="46">
         <f>IF($A10="","",YEAR($A10))</f>
         <v/>
       </c>
-      <c r="T10" s="41">
+      <c r="T10" s="46">
         <f>IF($A10="","",MONTH($A10))</f>
         <v/>
       </c>
-      <c r="U10" s="41">
+      <c r="U10" s="46">
         <f>IF($Q10="","",YEAR($Q10))</f>
         <v/>
       </c>
-      <c r="V10" s="41">
+      <c r="V10" s="46">
         <f>IF($Q10="","",MONTH($Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="26">
+      <c r="A11" s="43" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Servicio digital extranjero</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>Software y suscripciones</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>ManyChat · suscripción</t>
+        </is>
+      </c>
+      <c r="G11" s="45" t="n">
+        <v>36324</v>
+      </c>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I11" s="45">
         <f>IF($G11="","",IF(AND($H11="Sí",IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C11,Parámetros!$A$54:$A$60,0)),0)=1),ROUND($G11/(1+Parámetros!$B$13),0),$G11))</f>
         <v/>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="45">
         <f>IF($G11="","",IF(IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C11,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I11*Parámetros!$B$13,0),0))</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="45">
         <f>IF($G11="","",IF(IFERROR(INDEX(Parámetros!$C$54:$C$60,MATCH($C11,Parámetros!$A$54:$A$60,0)),0)=1,$J11,0))</f>
         <v/>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="45">
         <f>IF($G11="","",IF(IFERROR(INDEX(Parámetros!$D$54:$D$60,MATCH($C11,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I11*Parámetros!$B$16,0),0))</f>
         <v/>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="45">
         <f>IF($G11="","",$I11+$J11)</f>
         <v/>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="45">
         <f>IF($G11="","",$M11-$L11)</f>
         <v/>
       </c>
-      <c r="O11" s="35" t="n"/>
-      <c r="P11" s="35" t="n"/>
-      <c r="Q11" s="34" t="n"/>
-      <c r="R11" s="35" t="n"/>
-      <c r="S11" s="41">
+      <c r="O11" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P11" s="44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="Q11" s="43" t="n">
+        <v>46252</v>
+      </c>
+      <c r="R11" s="44" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+      <c r="S11" s="46">
         <f>IF($A11="","",YEAR($A11))</f>
         <v/>
       </c>
-      <c r="T11" s="41">
+      <c r="T11" s="46">
         <f>IF($A11="","",MONTH($A11))</f>
         <v/>
       </c>
-      <c r="U11" s="41">
+      <c r="U11" s="46">
         <f>IF($Q11="","",YEAR($Q11))</f>
         <v/>
       </c>
-      <c r="V11" s="41">
+      <c r="V11" s="46">
         <f>IF($Q11="","",MONTH($Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="26">
+      <c r="A12" s="43" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>Boleta de venta</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Equipamiento y hardware</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>Insumo de trabajo</t>
+        </is>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>18500</v>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I12" s="45">
         <f>IF($G12="","",IF(AND($H12="Sí",IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C12,Parámetros!$A$54:$A$60,0)),0)=1),ROUND($G12/(1+Parámetros!$B$13),0),$G12))</f>
         <v/>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="45">
         <f>IF($G12="","",IF(IFERROR(INDEX(Parámetros!$B$54:$B$60,MATCH($C12,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I12*Parámetros!$B$13,0),0))</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="45">
         <f>IF($G12="","",IF(IFERROR(INDEX(Parámetros!$C$54:$C$60,MATCH($C12,Parámetros!$A$54:$A$60,0)),0)=1,$J12,0))</f>
         <v/>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="45">
         <f>IF($G12="","",IF(IFERROR(INDEX(Parámetros!$D$54:$D$60,MATCH($C12,Parámetros!$A$54:$A$60,0)),0)=1,ROUND($I12*Parámetros!$B$16,0),0))</f>
         <v/>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="45">
         <f>IF($G12="","",$I12+$J12)</f>
         <v/>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="45">
         <f>IF($G12="","",$M12-$L12)</f>
         <v/>
       </c>
-      <c r="O12" s="35" t="n"/>
-      <c r="P12" s="35" t="n"/>
-      <c r="Q12" s="34" t="n"/>
-      <c r="R12" s="35" t="n"/>
-      <c r="S12" s="41">
+      <c r="O12" s="44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P12" s="44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="Q12" s="43" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R12" s="44" t="inlineStr">
+        <is>
+          <t>Tarjeta prepago</t>
+        </is>
+      </c>
+      <c r="S12" s="46">
         <f>IF($A12="","",YEAR($A12))</f>
         <v/>
       </c>
-      <c r="T12" s="41">
+      <c r="T12" s="46">
         <f>IF($A12="","",MONTH($A12))</f>
         <v/>
       </c>
-      <c r="U12" s="41">
+      <c r="U12" s="46">
         <f>IF($Q12="","",YEAR($Q12))</f>
         <v/>
       </c>
-      <c r="V12" s="41">
+      <c r="V12" s="46">
         <f>IF($Q12="","",MONTH($Q12))</f>
         <v/>
       </c>
@@ -31458,6 +31781,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -31475,8 +31799,9 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H6" s="47" t="inlineStr">
         <is>
           <t>Tu Impuesto Global Complementario (estimación)</t>
         </is>
@@ -31515,15 +31840,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="41">
+      <c r="A8" s="43" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>45214</v>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Cuenta personal · Gabriel Matamala</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>Retiro de utilidades</t>
+        </is>
+      </c>
+      <c r="E8" s="46">
         <f>IF($A8="","",YEAR($A8))</f>
         <v/>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="46">
         <f>IF($A8="","",MONTH($A8))</f>
         <v/>
       </c>
@@ -31538,15 +31875,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="41">
+      <c r="A9" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Cuenta personal · Gabriel Matamala</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>Retiro de utilidades</t>
+        </is>
+      </c>
+      <c r="E9" s="46">
         <f>IF($A9="","",YEAR($A9))</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="46">
         <f>IF($A9="","",MONTH($A9))</f>
         <v/>
       </c>
@@ -31561,38 +31910,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="41">
+      <c r="A10" s="43" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>Cuenta personal · Gabriel Matamala</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>Retiro de utilidades</t>
+        </is>
+      </c>
+      <c r="E10" s="46">
         <f>IF($A10="","",YEAR($A10))</f>
         <v/>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="46">
         <f>IF($A10="","",MONTH($A10))</f>
         <v/>
       </c>
-      <c r="H10" s="44" t="inlineStr">
-        <is>
-          <t>= Base bruta (renta a declarar)</t>
-        </is>
-      </c>
-      <c r="I10" s="45">
+      <c r="H10" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Base bruta (renta a declarar)</t>
+        </is>
+      </c>
+      <c r="I10" s="49">
         <f>I8+I9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="41">
+      <c r="A11" s="43" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Cuenta personal · Gabriel Matamala</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>Retiro de utilidades</t>
+        </is>
+      </c>
+      <c r="E11" s="46">
         <f>IF($A11="","",YEAR($A11))</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="46">
         <f>IF($A11="","",MONTH($A11))</f>
         <v/>
       </c>
@@ -31624,7 +31997,7 @@
           <t>Base en UTA</t>
         </is>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="50">
         <f>IFERROR(I10/I11,0)</f>
         <v/>
       </c>
@@ -31647,7 +32020,7 @@
           <t>Tasa del tramo</t>
         </is>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="51">
         <f>IFERROR(INDEX(Parámetros!$C$42:$C$49,MATCH(I12,Parámetros!$A$42:$A$49,1)),0)</f>
         <v/>
       </c>
@@ -31670,7 +32043,7 @@
           <t>Rebaja del tramo (UTA)</t>
         </is>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="50">
         <f>IFERROR(INDEX(Parámetros!$D$42:$D$49,MATCH(I12,Parámetros!$A$42:$A$49,1)),0)</f>
         <v/>
       </c>
@@ -31734,12 +32107,12 @@
         <f>IF($A17="","",MONTH($A17))</f>
         <v/>
       </c>
-      <c r="H17" s="44" t="inlineStr">
-        <is>
-          <t>= Te toca pagar (o te devuelven)</t>
-        </is>
-      </c>
-      <c r="I17" s="45">
+      <c r="H17" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Te toca pagar (o te devuelven)</t>
+        </is>
+      </c>
+      <c r="I17" s="49">
         <f>I15-I16</f>
         <v/>
       </c>
@@ -31860,7 +32233,7 @@
         <f>IF($A25="","",MONTH($A25))</f>
         <v/>
       </c>
-      <c r="H25" s="43" t="inlineStr">
+      <c r="H25" s="47" t="inlineStr">
         <is>
           <t>Cuánto puedes retirar sin descapitalizarte</t>
         </is>
@@ -31925,12 +32298,12 @@
         <f>IF($A28="","",MONTH($A28))</f>
         <v/>
       </c>
-      <c r="H28" s="44" t="inlineStr">
-        <is>
-          <t>= Margen que queda por retirar</t>
-        </is>
-      </c>
-      <c r="I28" s="45">
+      <c r="H28" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Margen que queda por retirar</t>
+        </is>
+      </c>
+      <c r="I28" s="49">
         <f>I26-I27</f>
         <v/>
       </c>
@@ -32552,6 +32925,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -32566,6 +32940,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -32696,11 +33071,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B8)</f>
         <v/>
       </c>
-      <c r="N8" s="45">
+      <c r="N8" s="49">
         <f>$I8+$L8+$M8</f>
         <v/>
       </c>
-      <c r="O8" s="48" t="inlineStr">
+      <c r="O8" s="52" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
@@ -32759,11 +33134,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B9)</f>
         <v/>
       </c>
-      <c r="N9" s="45">
+      <c r="N9" s="49">
         <f>$I9+$L9+$M9</f>
         <v/>
       </c>
-      <c r="O9" s="48" t="inlineStr">
+      <c r="O9" s="52" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
@@ -32822,11 +33197,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B10)</f>
         <v/>
       </c>
-      <c r="N10" s="45">
+      <c r="N10" s="49">
         <f>$I10+$L10+$M10</f>
         <v/>
       </c>
-      <c r="O10" s="48" t="inlineStr">
+      <c r="O10" s="52" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
@@ -32885,11 +33260,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B11)</f>
         <v/>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="49">
         <f>$I11+$L11+$M11</f>
         <v/>
       </c>
-      <c r="O11" s="48" t="inlineStr">
+      <c r="O11" s="52" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
@@ -32948,11 +33323,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B12)</f>
         <v/>
       </c>
-      <c r="N12" s="45">
+      <c r="N12" s="49">
         <f>$I12+$L12+$M12</f>
         <v/>
       </c>
-      <c r="O12" s="48" t="inlineStr">
+      <c r="O12" s="52" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
@@ -33011,11 +33386,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B13)</f>
         <v/>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="49">
         <f>$I13+$L13+$M13</f>
         <v/>
       </c>
-      <c r="O13" s="48" t="inlineStr">
+      <c r="O13" s="52" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
@@ -33074,11 +33449,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B14)</f>
         <v/>
       </c>
-      <c r="N14" s="45">
+      <c r="N14" s="49">
         <f>$I14+$L14+$M14</f>
         <v/>
       </c>
-      <c r="O14" s="48" t="inlineStr">
+      <c r="O14" s="52" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
@@ -33137,11 +33512,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B15)</f>
         <v/>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="49">
         <f>$I15+$L15+$M15</f>
         <v/>
       </c>
-      <c r="O15" s="48" t="inlineStr">
+      <c r="O15" s="52" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
@@ -33200,11 +33575,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B16)</f>
         <v/>
       </c>
-      <c r="N16" s="45">
+      <c r="N16" s="49">
         <f>$I16+$L16+$M16</f>
         <v/>
       </c>
-      <c r="O16" s="48" t="inlineStr">
+      <c r="O16" s="52" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
@@ -33263,11 +33638,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B17)</f>
         <v/>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="49">
         <f>$I17+$L17+$M17</f>
         <v/>
       </c>
-      <c r="O17" s="48" t="inlineStr">
+      <c r="O17" s="52" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
@@ -33326,11 +33701,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B18)</f>
         <v/>
       </c>
-      <c r="N18" s="45">
+      <c r="N18" s="49">
         <f>$I18+$L18+$M18</f>
         <v/>
       </c>
-      <c r="O18" s="48" t="inlineStr">
+      <c r="O18" s="52" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
@@ -33389,11 +33764,11 @@
         <f>SUMIFS(Gastos!$L$8:$L$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$V$8:$V$257,$B19)</f>
         <v/>
       </c>
-      <c r="N19" s="45">
+      <c r="N19" s="49">
         <f>$I19+$L19+$M19</f>
         <v/>
       </c>
-      <c r="O19" s="48" t="inlineStr">
+      <c r="O19" s="52" t="inlineStr">
         <is>
           <t>Enero del año siguiente</t>
         </is>
@@ -33405,7 +33780,7 @@
           <t>TOTAL AÑO</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n"/>
+      <c r="B20" s="53" t="n"/>
       <c r="C20" s="29">
         <f>SUM(C8:C19)</f>
         <v/>
@@ -33422,8 +33797,8 @@
         <f>SUM(F8:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="50" t="n"/>
-      <c r="H20" s="50" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="54" t="n"/>
       <c r="I20" s="29">
         <f>SUM(I8:I19)</f>
         <v/>
@@ -33448,8 +33823,9 @@
         <f>SUM(N8:N19)</f>
         <v/>
       </c>
-      <c r="O20" s="50" t="n"/>
-    </row>
+      <c r="O20" s="54" t="n"/>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -33512,13 +33888,16 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Determinación de la base imponible</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>Gastos pagados por categoría</t>
         </is>
@@ -33573,7 +33952,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E8)</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="51">
         <f>IFERROR($F8/$F$21,0)</f>
         <v/>
       </c>
@@ -33584,12 +33963,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>= Base imponible</t>
-        </is>
-      </c>
-      <c r="C9" s="45">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Base imponible</t>
+        </is>
+      </c>
+      <c r="C9" s="49">
         <f>C7+C8</f>
         <v/>
       </c>
@@ -33601,7 +33980,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E9)</f>
         <v/>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="51">
         <f>IFERROR($F9/$F$21,0)</f>
         <v/>
       </c>
@@ -33620,13 +33999,13 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E10)</f>
         <v/>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="51">
         <f>IFERROR($F10/$F$21,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>Impuesto de la empresa</t>
         </is>
@@ -33639,7 +34018,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E11)</f>
         <v/>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="51">
         <f>IFERROR($F11/$F$21,0)</f>
         <v/>
       </c>
@@ -33662,7 +34041,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E12)</f>
         <v/>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="51">
         <f>IFERROR($F12/$F$21,0)</f>
         <v/>
       </c>
@@ -33690,7 +34069,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E13)</f>
         <v/>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="51">
         <f>IFERROR($F13/$F$21,0)</f>
         <v/>
       </c>
@@ -33701,12 +34080,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>= Saldo a pagar en abril</t>
-        </is>
-      </c>
-      <c r="C14" s="45">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Saldo a pagar en abril</t>
+        </is>
+      </c>
+      <c r="C14" s="49">
         <f>C12+C13</f>
         <v/>
       </c>
@@ -33718,7 +34097,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E14)</f>
         <v/>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="51">
         <f>IFERROR($F14/$F$21,0)</f>
         <v/>
       </c>
@@ -33737,13 +34116,13 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E15)</f>
         <v/>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="51">
         <f>IFERROR($F15/$F$21,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>Qué queda para ti</t>
         </is>
@@ -33756,7 +34135,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E16)</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="51">
         <f>IFERROR($F16/$F$21,0)</f>
         <v/>
       </c>
@@ -33779,19 +34158,19 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E17)</f>
         <v/>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="51">
         <f>IFERROR($F17/$F$21,0)</f>
         <v/>
       </c>
       <c r="I17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>= Utilidad después de impuesto</t>
-        </is>
-      </c>
-      <c r="C18" s="45">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Utilidad después de impuesto</t>
+        </is>
+      </c>
+      <c r="C18" s="49">
         <f>C9-C12</f>
         <v/>
       </c>
@@ -33803,7 +34182,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E18)</f>
         <v/>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="51">
         <f>IFERROR($F18/$F$21,0)</f>
         <v/>
       </c>
@@ -33831,19 +34210,19 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E19)</f>
         <v/>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="51">
         <f>IFERROR($F19/$F$21,0)</f>
         <v/>
       </c>
       <c r="I19" s="23" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>= Utilidad que queda en la empresa</t>
-        </is>
-      </c>
-      <c r="C20" s="45">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Utilidad que queda en la empresa</t>
+        </is>
+      </c>
+      <c r="C20" s="49">
         <f>C18+C19</f>
         <v/>
       </c>
@@ -33855,7 +34234,7 @@
         <f>SUMIFS(Gastos!$M$8:$M$257,Gastos!$U$8:$U$257,Parámetros!$B$10,Gastos!$E$8:$E$257,$E20)</f>
         <v/>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="51">
         <f>IFERROR($F20/$F$21,0)</f>
         <v/>
       </c>
@@ -33866,7 +34245,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="51" t="inlineStr">
+      <c r="E21" s="55" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -33875,11 +34254,12 @@
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="56">
         <f>IFERROR(F21/F21,0)</f>
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -33916,7 +34296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33928,7 +34308,8 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -33945,6 +34326,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -33952,6 +34334,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -34023,7 +34407,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B8)</f>
         <v/>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="49">
         <f>$C8+$D8+$E8+$F8+$G8</f>
         <v/>
       </c>
@@ -34062,7 +34446,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B9)</f>
         <v/>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="49">
         <f>$C9+$D9+$E9+$F9+$G9</f>
         <v/>
       </c>
@@ -34096,7 +34480,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B10)</f>
         <v/>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="49">
         <f>$C10+$D10+$E10+$F10+$G10</f>
         <v/>
       </c>
@@ -34130,7 +34514,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B11)</f>
         <v/>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="49">
         <f>$C11+$D11+$E11+$F11+$G11</f>
         <v/>
       </c>
@@ -34164,7 +34548,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B12)</f>
         <v/>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="49">
         <f>$C12+$D12+$E12+$F12+$G12</f>
         <v/>
       </c>
@@ -34198,7 +34582,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B13)</f>
         <v/>
       </c>
-      <c r="H13" s="45">
+      <c r="H13" s="49">
         <f>$C13+$D13+$E13+$F13+$G13</f>
         <v/>
       </c>
@@ -34237,7 +34621,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B14)</f>
         <v/>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="49">
         <f>$C14+$D14+$E14+$F14+$G14</f>
         <v/>
       </c>
@@ -34271,7 +34655,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B15)</f>
         <v/>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="49">
         <f>$C15+$D15+$E15+$F15+$G15</f>
         <v/>
       </c>
@@ -34305,7 +34689,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B16)</f>
         <v/>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="49">
         <f>$C16+$D16+$E16+$F16+$G16</f>
         <v/>
       </c>
@@ -34339,7 +34723,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B17)</f>
         <v/>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="49">
         <f>$C17+$D17+$E17+$F17+$G17</f>
         <v/>
       </c>
@@ -34373,7 +34757,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B18)</f>
         <v/>
       </c>
-      <c r="H18" s="45">
+      <c r="H18" s="49">
         <f>$C18+$D18+$E18+$F18+$G18</f>
         <v/>
       </c>
@@ -34407,7 +34791,7 @@
         <f>-SUMIFS(Retiros!$B$8:$B$67,Retiros!$E$8:$E$67,Parámetros!$B$10,Retiros!$F$8:$F$67,$B19)</f>
         <v/>
       </c>
-      <c r="H19" s="45">
+      <c r="H19" s="49">
         <f>$C19+$D19+$E19+$F19+$G19</f>
         <v/>
       </c>
@@ -34418,8 +34802,8 @@
           <t>TOTAL AÑO</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="50" t="n"/>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="54" t="n"/>
       <c r="D20" s="29">
         <f>SUM(D8:D19)</f>
         <v/>
@@ -34436,15 +34820,77 @@
         <f>SUM(G8:G19)</f>
         <v/>
       </c>
-      <c r="H20" s="50" t="n"/>
-    </row>
+      <c r="H20" s="54" t="n"/>
+      <c r="J20" s="47" t="inlineStr">
+        <is>
+          <t>Conciliación con tu cuenta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Mes de corte (1 = enero, 12 = diciembre)</t>
+        </is>
+      </c>
+      <c r="K21" s="57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Saldo según esta planilla</t>
+        </is>
+      </c>
+      <c r="K22" s="26">
+        <f>INDEX($H$8:$H$19,$K$21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Saldo real de tu cuenta a esa fecha</t>
+        </is>
+      </c>
+      <c r="K23" s="36" t="n">
+        <v>799399</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> = Diferencia por explicar</t>
+        </is>
+      </c>
+      <c r="K24" s="49">
+        <f>K23-K22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>Si la diferencia no da cero, casi siempre es una de tres: (1) plata que entró y no es venta —un aporte tuyo o una recarga de la cuenta—; (2) impuestos que pagaste por un monto distinto al que estima la planilla; (3) un gasto que todavía no cargas. Los pagos al SII no se registran en Gastos a propósito: son el impuesto mismo, no un gasto, y aparecen arriba en la columna «Impuestos (F29)» ya calculados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="J20:K20"/>
     <mergeCell ref="J13:J17"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="J26:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
